--- a/results/Int All Data 0.7/Rando_fi_explain.xlsx
+++ b/results/Int All Data 0.7/Rando_fi_explain.xlsx
@@ -1676,466 +1676,466 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008333350394165795</v>
+        <v>0.0005964054993740367</v>
       </c>
       <c r="C3" t="n">
-        <v>-3.425633460056532e-05</v>
+        <v>-1.496164623438379e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0003841094277703994</v>
+        <v>5.68450500235984e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.490075899792617e-07</v>
+        <v>0.001058663631286881</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0001024097120421352</v>
+        <v>0.0002570280563554761</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001636237216352075</v>
+        <v>9.814536163140209e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0001475513878243495</v>
+        <v>0.0004107310472752045</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00115894130587378</v>
+        <v>0.000605449868827068</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.001098562638958115</v>
+        <v>-0.0006547289919115174</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0001246683158958694</v>
+        <v>1.803422746880723e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>4.163769770269554e-05</v>
+        <v>-0.000126853727422146</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0002708702093730952</v>
+        <v>0.0001271152667514242</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0009954921271456839</v>
+        <v>0.0002362745443829706</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001054116262379004</v>
+        <v>-0.0006040168500269438</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0001157216148877926</v>
+        <v>4.338791951570055e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.001533326347200488</v>
+        <v>0.001622518137096137</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0001686663562126079</v>
+        <v>-0.0004547923067967918</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008109901471434035</v>
+        <v>0.000918315115841305</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0001472143960995287</v>
+        <v>0.0003896901030478783</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0003026729799918282</v>
+        <v>4.330731717042124e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.001671866547102e-05</v>
+        <v>-0.0005094981709390801</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0001897376547592832</v>
+        <v>-0.0005501623781419818</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0001642506882887719</v>
+        <v>0.0004238483335172927</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.021607844390768e-06</v>
+        <v>0.0001884414149993707</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.456116727262095e-05</v>
+        <v>0.0008620934946287784</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0002714097204838439</v>
+        <v>-0.0005834063880404583</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0006784795092405194</v>
+        <v>-0.0004184141703158129</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.001764516111413695</v>
+        <v>-0.000738166210930814</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.001553228028178174</v>
+        <v>0.002741244963275927</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.004760674517844213</v>
+        <v>0.006506696128712649</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.0006154953820229614</v>
+        <v>-0.0006254268812234366</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.274010341485663e-05</v>
+        <v>0.000486815960063528</v>
       </c>
       <c r="AH3" t="n">
-        <v>8.476096535855459e-05</v>
+        <v>0.0004116676668518049</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.0002710884635082912</v>
+        <v>0.0008688957172994383</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.004149192759443639</v>
+        <v>0.00424070199469863</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.009081688012601457</v>
+        <v>0.006957762311603405</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0003927186904784407</v>
+        <v>0.0002687033843773434</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.004307225414782281</v>
+        <v>0.0053265448482146</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.0003242714111892243</v>
+        <v>-0.001485837253076045</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.001483792981135901</v>
+        <v>0.001325320721887132</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.0002925015495196382</v>
+        <v>-4.865078509232346e-05</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.0001011180530854793</v>
+        <v>-0.00019432959145949</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.006752446157337962</v>
+        <v>0.007797668199377661</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.0003319531213308325</v>
+        <v>8.476066293952033e-05</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.00163432219793092</v>
+        <v>-8.863944820985742e-05</v>
       </c>
       <c r="AU3" t="n">
-        <v>-8.719042195654885e-05</v>
+        <v>-0.0001025588934562716</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.001087114133568719</v>
+        <v>-0.0004205025496400882</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.000347707899032189</v>
+        <v>-0.0007425349662667146</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.0001378392060716116</v>
+        <v>0.0001073516764657911</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.001761529464802286</v>
+        <v>-0.0008051461502518653</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.0003608583440362622</v>
+        <v>7.170209829109207e-05</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.0008259119280005656</v>
+        <v>0.000806672916746135</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.002056196012944683</v>
+        <v>-0.0006669653080105942</v>
       </c>
       <c r="BC3" t="n">
-        <v>-8.017971615976726e-05</v>
+        <v>-2.275626017087196e-05</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.0002593957198052233</v>
+        <v>-8.112434354046516e-05</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.00126853242509008</v>
+        <v>-0.0005438935707092207</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.0002796057492195169</v>
+        <v>-0.00179620504154195</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.0003058152544804195</v>
+        <v>-0.0004227230109773394</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.0002411243666795925</v>
+        <v>0.0001794349805164708</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.001155326602020495</v>
+        <v>0.001712698570318788</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0003700949278032396</v>
+        <v>-0.001016056571765288</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.0004928598757927019</v>
+        <v>0.001134807611823847</v>
       </c>
       <c r="BL3" t="n">
-        <v>2.011523814228202e-05</v>
+        <v>-4.635825925076942e-05</v>
       </c>
       <c r="BM3" t="n">
-        <v>-7.760569373009614e-05</v>
+        <v>-0.0004827902752555635</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.0001301678466926115</v>
+        <v>6.043720841665159e-05</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0.001419719387249765</v>
+        <v>-0.0006622395477638565</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.0002127401865553257</v>
+        <v>-0.003529922129476682</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0.0005082909691204352</v>
+        <v>-0.000384451758255363</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.0002491749071043559</v>
+        <v>0.0006133813199927596</v>
       </c>
       <c r="BT3" t="n">
-        <v>-5.37005942382085e-05</v>
+        <v>0.0005037061294344425</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.002182548191147705</v>
+        <v>-0.00228716849908521</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.001638234595658867</v>
+        <v>0.0004109405757853735</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.697453755260986e-05</v>
+        <v>4.709576138148264e-05</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0.001013318746369659</v>
+        <v>-0.000701379431820104</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.0003526380639949045</v>
+        <v>0.0005870365338777084</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.001499346505223915</v>
+        <v>0.0008188034548401966</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.0003749709726459849</v>
+        <v>-6.573389907699135e-06</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0.000759035563126148</v>
+        <v>-0.0004623777756372471</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.0004058888852506582</v>
+        <v>-0.0001344885396597539</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.0001505765823082205</v>
+        <v>0.000649387700416506</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.0007581880230865445</v>
+        <v>-0.000823605231219119</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.001078170817695838</v>
+        <v>-0.0003445185248801019</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.0005730245219237262</v>
+        <v>-0.001517754592077142</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0002829045529958296</v>
+        <v>0.000255913874302336</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.001041546645746195</v>
+        <v>-0.001665087854621079</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-5.232862375719183e-06</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.0006495814622141993</v>
+        <v>0.0004331295651439448</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0.001146515131327995</v>
+        <v>0.0001962668462815487</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.0001801553883231255</v>
+        <v>0.0001110391699646529</v>
       </c>
       <c r="CN3" t="n">
-        <v>9.837549852353851e-05</v>
+        <v>2.577703709209511e-05</v>
       </c>
       <c r="CO3" t="n">
-        <v>-0.0002119101143620461</v>
+        <v>-0.0005495862778433625</v>
       </c>
       <c r="CP3" t="n">
-        <v>-0.0001223695497193267</v>
+        <v>-0.0001001173972460912</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.0003548664101401955</v>
+        <v>-0.0001511981416785357</v>
       </c>
       <c r="CR3" t="n">
-        <v>-8.361751057713195e-05</v>
+        <v>-0.0005204991642431623</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0.0007705498482075801</v>
+        <v>-0.0003292603706905262</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0.001362079989983938</v>
+        <v>-0.0004090872413294778</v>
       </c>
       <c r="CU3" t="n">
-        <v>-9.46620438735879e-05</v>
+        <v>0.0002795358325925224</v>
       </c>
       <c r="CV3" t="n">
-        <v>-4.275788348476971e-05</v>
+        <v>-5.822969575633995e-06</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.0001115918549024886</v>
+        <v>-0.0007366498753606375</v>
       </c>
       <c r="CY3" t="n">
-        <v>-0.001319460478763201</v>
+        <v>0.0001542887813995619</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.0002112313240597586</v>
+        <v>-5.537487357542004e-06</v>
       </c>
       <c r="DA3" t="n">
-        <v>8.577481038752884e-06</v>
+        <v>-2.611446195154632e-05</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0.0002509052884946616</v>
+        <v>-0.000217609751669301</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0.001752610495527049</v>
+        <v>-0.001192325616963977</v>
       </c>
       <c r="DD3" t="n">
-        <v>-2.960771774759063e-05</v>
+        <v>1.743687398307103e-05</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.0002163178820751977</v>
+        <v>9.331735994471457e-05</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.0009735855556913031</v>
+        <v>-0.0002475370598264137</v>
       </c>
       <c r="DG3" t="n">
-        <v>-6.151345239062129e-05</v>
+        <v>-0.0002335664158192374</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0.001538974331377449</v>
+        <v>-0.0017879838889091</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.001199029408299373</v>
+        <v>0.0001195622623913284</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.00011244904640768</v>
+        <v>-9.127801552240021e-05</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0.0003259592954437207</v>
+        <v>-1.518307340223611e-06</v>
       </c>
       <c r="DL3" t="n">
-        <v>-5.980538442719064e-05</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0.0002266740500379794</v>
+        <v>-0.0003286618759646298</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.001665445882253978</v>
+        <v>-0.0005400812189557336</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.001346506701402411</v>
+        <v>-0.0006858154583564058</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.001190022464421191</v>
+        <v>-0.0004035182096422951</v>
       </c>
       <c r="DQ3" t="n">
-        <v>1.134636107093745e-05</v>
+        <v>2.15047515219513e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.068695504151124e-05</v>
+        <v>5.151983513652647e-06</v>
       </c>
       <c r="DS3" t="n">
-        <v>5.325419241015374e-05</v>
+        <v>5.896356552224535e-05</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0.0005507797522662373</v>
+        <v>0.0005813530027037328</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0.0007317652641088069</v>
+        <v>-0.0006295140610849093</v>
       </c>
       <c r="DV3" t="n">
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>7.626862504517274e-07</v>
+        <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.0001238908190761112</v>
+        <v>6.907086952720463e-05</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.002713078453658153</v>
+        <v>-0.001546055746507554</v>
       </c>
       <c r="DZ3" t="n">
-        <v>1.997499084503196e-05</v>
+        <v>3.227950133024571e-05</v>
       </c>
       <c r="EA3" t="n">
-        <v>7.099644300804676e-05</v>
+        <v>-0.0002638751822161845</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.0004728763763733567</v>
+        <v>0.000753895813357135</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.0001071046722230151</v>
+        <v>0.0004522243801303028</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0.0004651524532136097</v>
+        <v>-8.453251157380381e-05</v>
       </c>
       <c r="EE3" t="n">
-        <v>-1.569858712715755e-05</v>
+        <v>3.606388459556853e-05</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.0007581182972394551</v>
+        <v>-0.0001370158824471979</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.0001546617084526492</v>
+        <v>4.699315832901618e-05</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0.0003619169807562617</v>
+        <v>-3.172995971000181e-05</v>
       </c>
       <c r="EI3" t="n">
-        <v>-5.831581606871019e-06</v>
+        <v>4.616535409207145e-05</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.0001301560733979923</v>
+        <v>2.188730230779811e-05</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.0002851275482703851</v>
+        <v>-2.023848695322461e-05</v>
       </c>
       <c r="EL3" t="n">
-        <v>5.232862375720293e-06</v>
+        <v>0</v>
       </c>
       <c r="EM3" t="n">
-        <v>3.691577114541045e-05</v>
+        <v>-9.794486392176174e-06</v>
       </c>
       <c r="EN3" t="n">
-        <v>-5.768318287193042e-05</v>
+        <v>-1.669742272463748e-05</v>
       </c>
       <c r="EO3" t="n">
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>6.942365713260567e-05</v>
+        <v>-1.620806042224032e-05</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.0001826179270487882</v>
+        <v>0.0001122347469139418</v>
       </c>
       <c r="ER3" t="n">
-        <v>-5.151983513652647e-06</v>
+        <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-1.136070923044797e-05</v>
+        <v>2.030128131784048e-05</v>
       </c>
       <c r="ET3" t="n">
-        <v>-4.93647445144507e-05</v>
+        <v>-8.79124673722198e-05</v>
       </c>
       <c r="EU3" t="n">
-        <v>-6.360751166923472e-05</v>
+        <v>0.0004846704741315644</v>
       </c>
       <c r="EV3" t="n">
-        <v>-3.693931398416783e-05</v>
+        <v>1.116330493619255e-05</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0.000440490173047544</v>
+        <v>-0.0001595381077464209</v>
       </c>
       <c r="EX3" t="n">
-        <v>-4.18705195271307e-05</v>
+        <v>7.468642188969254e-05</v>
       </c>
       <c r="EY3" t="n">
-        <v>7.999479415388156e-07</v>
+        <v>7.490359035800974e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2145,466 +2145,466 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004350062670271672</v>
+        <v>0.0055974758503233</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0001809709262609057</v>
+        <v>0.0002422067232838015</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001472150740949833</v>
+        <v>0.0004064018622296322</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001981863274435296</v>
+        <v>0.0022698101219303</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0006303277853464756</v>
+        <v>0.0008886242105862383</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001480721723587941</v>
+        <v>0.003298918111231534</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002028738201856909</v>
+        <v>0.002658336343212734</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003991377940656454</v>
+        <v>0.001778424287890275</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002822161808125829</v>
+        <v>0.003414538815681421</v>
       </c>
       <c r="K4" t="n">
-        <v>0.000980488002830423</v>
+        <v>0.0001655341031687941</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003658937291315546</v>
+        <v>0.000303098119776329</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001245927091256811</v>
+        <v>0.002186545481806195</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002608108784488858</v>
+        <v>0.004303805330119805</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002242528344201522</v>
+        <v>0.002280940972120068</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001569172745890539</v>
+        <v>0.0006732627850391628</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.003269926818122274</v>
+        <v>0.003561831227218023</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002724644019093185</v>
+        <v>0.001180056156813696</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003385007284823209</v>
+        <v>0.002554037265895149</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0003861782313788951</v>
+        <v>0.001180500971048989</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0008457970329216394</v>
+        <v>0.001252805977530291</v>
       </c>
       <c r="V4" t="n">
-        <v>0.00169312308879237</v>
+        <v>0.002410055099214877</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0009039493384150316</v>
+        <v>0.002746907474735927</v>
       </c>
       <c r="X4" t="n">
-        <v>0.003817795471875351</v>
+        <v>0.004966322174006841</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0002446136439569908</v>
+        <v>0.000534199130099851</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00156200452733268</v>
+        <v>0.002758174621892094</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002482313436088544</v>
+        <v>0.003743020776723563</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001234175466759146</v>
+        <v>0.001925531628672347</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.004815283366982709</v>
+        <v>0.002574266114549442</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.008201363885131716</v>
+        <v>0.008033716942474886</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.004295317593675472</v>
+        <v>0.006025720808962349</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.002912401749156775</v>
+        <v>0.002684182191211523</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001484116213839202</v>
+        <v>0.0008267343249787541</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0006595126486699322</v>
+        <v>0.0007118277787201862</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.001972414174931524</v>
+        <v>0.00127133969728675</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.003335113315164309</v>
+        <v>0.006224544570205865</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01351056507964348</v>
+        <v>0.0112752202844779</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001355427988860092</v>
+        <v>0.001299638417163516</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.01547317002615706</v>
+        <v>0.01499153310944746</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.002742759925173462</v>
+        <v>0.004890776409584342</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.001580964289813619</v>
+        <v>0.002584181553497168</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.00124636892714686</v>
+        <v>0.0004295187626735957</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.001961804279638849</v>
+        <v>0.003096024437810317</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.005373518848398927</v>
+        <v>0.007767725509597033</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.0004472016164369948</v>
+        <v>0.0004472631527484463</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.002298616284574847</v>
+        <v>0.0008823711419107767</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.001089507085075814</v>
+        <v>0.0009318352006152247</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.001903785295639139</v>
+        <v>0.0009013426745380849</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.003916957229988209</v>
+        <v>0.002090868283582104</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0003955690941295869</v>
+        <v>0.0004344588593167374</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.003624157444595301</v>
+        <v>0.003484274043167528</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.001751886979699181</v>
+        <v>0.001133171549679078</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.00320493046570452</v>
+        <v>0.002385467531974513</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.007187056786603511</v>
+        <v>0.007107757752836635</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0002389058805097071</v>
+        <v>0.000395311489582451</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0005255523673736043</v>
+        <v>0.0003093114235954779</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.001939919226115333</v>
+        <v>0.001496675710258685</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.004044647786051616</v>
+        <v>0.006870271139626721</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.002634891119214575</v>
+        <v>0.001537757905262522</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0008928042037758602</v>
+        <v>0.0006583171324586386</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.008065293406423658</v>
+        <v>0.006219020969068604</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.003713613753107763</v>
+        <v>0.004098347573479598</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.003668826295189716</v>
+        <v>0.002277511928623946</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.001135582770909567</v>
+        <v>0.0003336402862384415</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.002546402890724757</v>
+        <v>0.002243707485375692</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.002786748390254924</v>
+        <v>0.002712254420048122</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.002300522544667528</v>
+        <v>0.002337656374627907</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.004966653772630684</v>
+        <v>0.01170602761111591</v>
       </c>
       <c r="BQ4" t="n">
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.003629450064069933</v>
+        <v>0.001103845171641876</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.003896970806123633</v>
+        <v>0.001154739965683773</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.0009351037083297568</v>
+        <v>0.0009449787120245937</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.006501600646272918</v>
+        <v>0.007616448302931522</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.003143445353503473</v>
+        <v>0.0007758039271164109</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0003898445002841788</v>
+        <v>0.0001489298741052832</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.003492345349839703</v>
+        <v>0.001741341210518137</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.003033241053222946</v>
+        <v>0.001744506420751824</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.003048515570859454</v>
+        <v>0.001528624269385987</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.001237802968662525</v>
+        <v>0.001377905746236456</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.00471385732802725</v>
+        <v>0.002656626854443891</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.003135682565145327</v>
+        <v>0.001559492370099105</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.003827948422124304</v>
+        <v>0.001132459679935366</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.002190778181897157</v>
+        <v>0.002750032996893054</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.002630617955295765</v>
+        <v>0.001957160297348431</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.003017367453141751</v>
+        <v>0.004620663707180146</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001353447426376231</v>
+        <v>0.0008747124054400729</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.003814509293445512</v>
+        <v>0.006793967411656142</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>1.654776378947241e-05</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.001542098142764988</v>
+        <v>0.0009723048861513071</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.002710685615893911</v>
+        <v>0.002714216787566086</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.001207279205149938</v>
+        <v>0.000319133493033017</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0008818676216252683</v>
+        <v>0.0003194137775582698</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.0008453869709403226</v>
+        <v>0.001482258605049223</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0002710955496606715</v>
+        <v>0.0006346195221808414</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.001315636104124514</v>
+        <v>0.0005340241733737966</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.003857689401103355</v>
+        <v>0.0009967766144978508</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.003170595846105185</v>
+        <v>0.003305263697037935</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.001873457106692166</v>
+        <v>0.00174090117579247</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0001829847592664625</v>
+        <v>0.0005987903317383074</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0001176381544216642</v>
+        <v>6.452847315754733e-05</v>
       </c>
       <c r="CW4" t="n">
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.002532153639344103</v>
+        <v>0.002354789820668062</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.002288298051985751</v>
+        <v>0.0008599297530102821</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0006679720972019619</v>
+        <v>3.912108624479952e-05</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0002763902555923138</v>
+        <v>0.0001923559997387215</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.0007846040862178543</v>
+        <v>0.000962394327021494</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.003858051155605964</v>
+        <v>0.003198521714035514</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0001498406094314904</v>
+        <v>0.0001805426472775041</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.0007767442845586475</v>
+        <v>0.0003773412642356756</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.001371963595165736</v>
+        <v>0.0009099982228995691</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.0009504160135406778</v>
+        <v>0.001102010834202272</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.001892518706625484</v>
+        <v>0.006442314616404605</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.003958270183414176</v>
+        <v>0.002265713020714326</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.001529779586850067</v>
+        <v>0.0005712547551107748</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.001398205593778236</v>
+        <v>0.0006420890142719396</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0001552406501495829</v>
+        <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.001443427340486044</v>
+        <v>0.0007642539806773382</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.002969205108464318</v>
+        <v>0.00148303764447536</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.006382957716688452</v>
+        <v>0.0020093639860623</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.003786671872670752</v>
+        <v>0.003168413680805272</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9.631753360483766e-05</v>
+        <v>6.732228735500472e-05</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0003142111799685418</v>
+        <v>1.629200237077956e-05</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0002738628870212526</v>
+        <v>0.0001607218987071996</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.002359947551504208</v>
+        <v>0.002314630825329467</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.003419849679397419</v>
+        <v>0.002995645753465251</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>7.341722093924837e-05</v>
+        <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.001550961565854669</v>
+        <v>0.0001406636094225246</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.005773349190028854</v>
+        <v>0.003180838915907977</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0001524639938197236</v>
+        <v>0.0001429162469772938</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.0009213746839773643</v>
+        <v>0.001279662640421247</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.003070718099953735</v>
+        <v>0.002265839960462524</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.001918401482840575</v>
+        <v>0.002147852759363699</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.001527905824506755</v>
+        <v>0.0004215886783614605</v>
       </c>
       <c r="EE4" t="n">
-        <v>4.964329136841721e-05</v>
+        <v>0.0001140440165954569</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.001340352015777003</v>
+        <v>0.000361258709070695</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.0004181554798070282</v>
+        <v>0.0001000017395979947</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0009279193804854751</v>
+        <v>8.327112495186141e-05</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.001004377258798686</v>
+        <v>0.0004731625303428605</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0005480809451279667</v>
+        <v>0.0003111822177695064</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.001670835124202744</v>
+        <v>0.0001502598236332708</v>
       </c>
       <c r="EL4" t="n">
-        <v>1.654776378947591e-05</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>7.105055471214202e-05</v>
+        <v>0.0001754768805396029</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0001807613189866695</v>
+        <v>6.940254038922525e-05</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0001663655320925155</v>
+        <v>5.096032608998671e-05</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.001161449320984874</v>
+        <v>0.0005119437649460897</v>
       </c>
       <c r="ER4" t="n">
-        <v>1.629200237077956e-05</v>
+        <v>0</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0001764184602280583</v>
+        <v>0.0001900963864174939</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.000314824910163243</v>
+        <v>0.0005470932215318393</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.001242176572593169</v>
+        <v>0.0008272619186992297</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0001168123673940794</v>
+        <v>0.0001674403725326333</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.001123912101828235</v>
+        <v>0.0003026286787291385</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0007130057511395356</v>
+        <v>0.0002029012753129828</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.0001650038721417062</v>
+        <v>0.0005489461229859553</v>
       </c>
     </row>
     <row r="5">
@@ -2614,466 +2614,466 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.004756814537680431</v>
+        <v>-0.01015499732763231</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0005232862375719072</v>
+        <v>-0.0003206841261357174</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.001952506596306114</v>
+        <v>-0.000903294367693952</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.003012048192771133</v>
+        <v>-0.0003869541182974001</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.001763762693746662</v>
+        <v>-0.001222104144527136</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0001046572475143503</v>
+        <v>-0.00785676109032608</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.003760947964966543</v>
+        <v>-0.006092998396579419</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.004970603955104247</v>
+        <v>-0.002405130946018219</v>
       </c>
       <c r="J5" t="n">
         <v>-0.008284339925173745</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.001445783132530143</v>
+        <v>-0.0002137894174238042</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0006860158311345566</v>
+        <v>-0.0005844845908607899</v>
       </c>
       <c r="M5" t="n">
+        <v>-0.005398182789951922</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.004329235702832668</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.006520577231427072</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.0006697578567748553</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.003506907545164717</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.00304649919828972</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.002084446819882446</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.000106894708711891</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.00208444681988238</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.005825761624799608</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.008177445216461831</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.009406734366648906</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.0005667181865017911</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0.004436130411544581</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-0.009887760555852531</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.005825761624799608</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0.006199893105291321</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.004994686503719458</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-0.002832709780865794</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.00646712987707102</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-0.0002060793405461059</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.0005879208979155948</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.0001105583195135429</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0.00732228754676646</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0.008070550507749819</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0.001122394441475094</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-0.006253340459647205</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0.01400320684126139</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.0008433734939758631</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-0.001236476043276635</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.007803313735970097</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.002405130946018142</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-0.0004810261892036815</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-0.001381509032943684</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0.002030999465526429</v>
+      </c>
+      <c r="AV5" t="n">
         <v>-0.002565473009086083</v>
       </c>
-      <c r="N5" t="n">
-        <v>-0.004115446285408908</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-0.003153393907001645</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.003955104222341033</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.006110520722635448</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-0.004518072289156671</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-0.005718866916087651</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.0008349705304518951</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-0.002030999465526473</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-0.002244788882950322</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-0.0008017103153394323</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.007048192771084372</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-0.0005527915975677145</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-0.002191341528594337</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-0.003373493975903652</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-0.0001583113456464336</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-0.01181186531266707</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-0.01060686015831138</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-0.001686746987951837</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-0.005986103687867494</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-0.002231668437832046</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-0.0006626506024096978</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-0.004703367183324436</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-0.009458023379383607</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>-0.001496525921966874</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-0.007322287546766481</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-0.005065963060686063</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>-0.001009564293304954</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-0.002779262426509932</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-0.004096385542168723</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-4.440892098500626e-17</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-0.00111583421891599</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>-0.0006376195536662799</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>-0.002084446819882435</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-0.006039551042223423</v>
-      </c>
       <c r="AW5" t="n">
-        <v>-0.009567076429716759</v>
+        <v>-0.005398182789951855</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.001160949868073891</v>
+        <v>-0.0006332453825857343</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.009815303430079202</v>
+        <v>-0.00871191876002142</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.003848209513629097</v>
+        <v>-0.002298236237306284</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.003046499198289698</v>
+        <v>-0.003045186640471487</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.005665419561731733</v>
+        <v>-0.01266702298236242</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.0004420432220039738</v>
+        <v>-0.0007915567282321678</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>-0.0005879208979155948</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.004749340369393151</v>
+        <v>-0.004371316306483286</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.004091392136025463</v>
+        <v>-0.01699625868519511</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.004222340994120821</v>
+        <v>-0.003741314804917184</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.001817210048102658</v>
+        <v>-0.0003741314804917905</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.009834313201496581</v>
+        <v>-0.003045186640471475</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.007108498129342633</v>
+        <v>-0.01058257616248002</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.003794762159273157</v>
+        <v>-0.0006907545164718476</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.00162650602409643</v>
+        <v>-0.0004810261892036594</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.005237840726884024</v>
+        <v>-0.004329235702832735</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.003746701846965717</v>
+        <v>-0.004666011787819235</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.006948156066274769</v>
+        <v>-0.006841261357562856</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.01101015499732765</v>
+        <v>-0.03682522715125595</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.01004810261892039</v>
+        <v>-0.00176376269374664</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.01026189203634422</v>
+        <v>-0.0007438894792773598</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.001965993623804452</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.02020309994655266</v>
+        <v>-0.02394441475146974</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.008498129342597537</v>
+        <v>-0.0008551576696953167</v>
       </c>
       <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>-0.005024051309460165</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>-0.001763762693746618</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>-0.0006376195536663354</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>-0.002886157135221856</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>-0.007642971672902166</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>-0.003634420096205282</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>-0.0007186290768380288</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>-0.007856761090325981</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>-0.00582576162479953</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>-0.01453768038482092</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>-0.001015499732763259</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>-0.02079102084446815</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>-5.232862375719183e-05</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>-0.001203558346415423</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>-0.006199893105291243</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>-0.0003188097768331621</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>-0.0005402750491158792</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>-0.00475681453768041</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>-0.0017516743946419</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>-0.0008501594048884286</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>-0.00230245944531654</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>-0.009299839657936904</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>-0.005184393372528018</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>-0.0001105583195135429</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>-0.007215392838054479</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>-0.0008844665561083432</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>-0.0001068947087119465</v>
+      </c>
+      <c r="DA5" t="n">
         <v>-0.0004749340369393007</v>
       </c>
-      <c r="BX5" t="n">
-        <v>-0.01074291822554784</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>-0.003099946552645683</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>-0.007831325301204849</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>-0.001385542168674736</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>-0.01400320684126136</v>
-      </c>
-      <c r="CC5" t="n">
-        <v>-0.008818813468733311</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>-0.005843373493975934</v>
-      </c>
-      <c r="CE5" t="n">
-        <v>-0.006626506024096435</v>
-      </c>
-      <c r="CF5" t="n">
-        <v>-0.008284339925173722</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>-0.008711918760021387</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>-0.001445783132530165</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>-0.01149118118653126</v>
-      </c>
-      <c r="CJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>-0.004543025120256561</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>-0.006039551042223423</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>-0.001424361493123794</v>
-      </c>
-      <c r="CN5" t="n">
-        <v>-0.001282736504543069</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>-0.002228915662650643</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>-0.0008551576696953945</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>-0.002409638554216908</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>-0.006360235168359207</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>-0.007161945483698573</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>-0.004329235702832712</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>-0.0005277044854881119</v>
-      </c>
-      <c r="CV5" t="n">
-        <v>-0.000374131480491735</v>
-      </c>
-      <c r="CW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX5" t="n">
-        <v>-0.005718866916087706</v>
-      </c>
-      <c r="CY5" t="n">
-        <v>-0.006146445750935347</v>
-      </c>
-      <c r="CZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA5" t="n">
-        <v>-0.0005421686746988619</v>
-      </c>
       <c r="DB5" t="n">
-        <v>-0.001817288801571726</v>
+        <v>-0.002886157135221845</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0.01165152324959916</v>
+        <v>-0.01010154997327628</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0.0003206841261357729</v>
+        <v>-0.0002093144950287673</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0.0007482629609834701</v>
+        <v>-0.0005879208979155837</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.004382683057188708</v>
+        <v>-0.001700154559505374</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0.00206079340546117</v>
+        <v>-0.002009273570324566</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.004675876726886241</v>
+        <v>-0.01924104756814533</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.008711918760021387</v>
+        <v>-0.003687867450561155</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.004116094986807395</v>
+        <v>-0.001389631213254983</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0.002832709780865861</v>
+        <v>-0.0007326007326006855</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0.0004911591355599709</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0.002108433734939808</v>
+        <v>-0.00219134152859437</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0.008711918760021397</v>
+        <v>-0.003848209513629042</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.01859967931587387</v>
+        <v>-0.004756814537680343</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0.01004810261892039</v>
+        <v>-0.008765366114377282</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.0001046572475143837</v>
+        <v>-0.0001055408970976224</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.0001569858712715755</v>
+        <v>0</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.0004810261892036594</v>
+        <v>-0.000180722891566254</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.006574024585783012</v>
+        <v>-0.001870657402458553</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0.009460181721004846</v>
+        <v>-0.006734366648850842</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0.0001473477406679913</v>
+        <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.00271084337349401</v>
+        <v>-0.0001030396702730529</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0.01769107429182257</v>
+        <v>-0.007749866381614068</v>
       </c>
       <c r="DZ5" t="n">
         <v>-0.0002672367717798108</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.002191341528594348</v>
+        <v>-0.002618920363441956</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.008177445216461809</v>
+        <v>-0.002060793405461136</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0.003674698795180775</v>
+        <v>-0.004008551576696917</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0.004538258575197895</v>
+        <v>-0.0008551576696953945</v>
       </c>
       <c r="EE5" t="n">
-        <v>-0.0001569858712715755</v>
+        <v>0</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0.003072289156626551</v>
+        <v>-0.0008551576696953945</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.001336183858898987</v>
+        <v>0</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0.002590361445783174</v>
+        <v>-0.0002638522427440559</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.002030999465526462</v>
+        <v>-0.0006860158311345454</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.001443078567610911</v>
+        <v>-0.0003741314804917573</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0.004749340369393151</v>
+        <v>-0.0002638522427440559</v>
       </c>
       <c r="EL5" t="n">
         <v>0</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0.0004186289900575346</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0.0004810261892036594</v>
+        <v>-0.0001583113456464336</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0</v>
+        <v>-0.0001105583195135429</v>
       </c>
       <c r="EQ5" t="n">
-        <v>-0.002730551262236014</v>
+        <v>-0.000694815606627508</v>
       </c>
       <c r="ER5" t="n">
-        <v>-5.151983513652647e-05</v>
+        <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.0004275788348476972</v>
+        <v>-0.0002763957987838572</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0.0006907545164717921</v>
+        <v>-0.001282736504542981</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.002244788882950299</v>
+        <v>-0.0004749340369393007</v>
       </c>
       <c r="EV5" t="n">
         <v>-0.0003693931398416783</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0.00343373493975907</v>
+        <v>-0.0008501594048884286</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.001603420630678831</v>
+        <v>-0.0002763957987838572</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.0003614457831325857</v>
+        <v>-0.001122394441475205</v>
       </c>
     </row>
     <row r="6">
@@ -3083,298 +3083,298 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-4.958196228056488e-05</v>
+        <v>-0.0003463712494915727</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>-0.0001603420630679114</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1.336183858897944e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0003607696419027278</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003952664700302005</v>
+        <v>-0.0003838610402600945</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0009198142259728426</v>
+        <v>1.6687575449173e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0008542417669949648</v>
+        <v>-0.000117085122961097</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.001522106598494488</v>
+        <v>-0.000425207828663543</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0002238140672987027</v>
+        <v>-7.970244420830164e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>-8.017103153394324e-05</v>
+        <v>-0.0004075046126660653</v>
       </c>
       <c r="M6" t="n">
-        <v>1.336183858899054e-05</v>
+        <v>-0.0001034436017224194</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.002806696084484283</v>
+        <v>-0.002724643603839829</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0003482500284206408</v>
+        <v>-0.0001620411338126932</v>
       </c>
       <c r="P6" t="n">
-        <v>5.313496280553165e-05</v>
+        <v>-0.0003807908720966147</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.004042527135820356</v>
+        <v>-0.0008835665602890202</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.0008287835954367384</v>
+        <v>-0.0006238801701440421</v>
       </c>
       <c r="S6" t="n">
-        <v>4.940711462450009e-05</v>
+        <v>-0.0003172016291197122</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.000297808014527412</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0006197777356972467</v>
+        <v>-0.0002201768078720245</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.001187125713068396</v>
+        <v>-4.145936981757859e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0004231075080780577</v>
+        <v>-0.0001636245772706296</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.001720103202793805</v>
+        <v>-0.0006580949246025147</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0005691644466939066</v>
+        <v>6.784459409198418e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.0006391900960455721</v>
+        <v>-0.001120556414219467</v>
       </c>
       <c r="AB6" t="n">
-        <v>-3.683693516701725e-05</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.003303696120434619</v>
+        <v>-0.001590485373380657</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.002360818519658217</v>
+        <v>-0.003844052438689308</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.002887496844631759</v>
+        <v>0.003158548787546678</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.00268826279297604</v>
+        <v>-0.001046373832366579</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0006699595910691108</v>
+        <v>-4.008551576694663e-05</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0002636559044413761</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.000491318096107149</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.002039446685911431</v>
+        <v>0.000190298084015822</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.00184121170751343</v>
+        <v>-0.0008584337349397176</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0001503770292286377</v>
+        <v>-0.0006454898144233667</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.002453676825064408</v>
+        <v>-0.0007832046521437069</v>
       </c>
       <c r="AN6" t="n">
-        <v>-8.017103153394324e-05</v>
+        <v>-0.002365487229383162</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.0004645613964980727</v>
+        <v>-0.0004744263575839319</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0005770357471531512</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-3.683693516699782e-05</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.003541802147604167</v>
+        <v>0.001951844649072818</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.0006015081169144981</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.0003082848645332397</v>
+        <v>-0.0005848443887689819</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.0008104125736738854</v>
+        <v>-0.0003141869649358087</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.001280850991606236</v>
+        <v>-0.0004789276711834545</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.0002251152398135336</v>
+        <v>-0.001850303497627323</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0001734242190071789</v>
+        <v>-7.84929356357794e-05</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.00328008497644805</v>
+        <v>-0.002061641776398846</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.001346664633077113</v>
+        <v>-0.000178919635209604</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.002091547279755343</v>
+        <v>-7.915567282321679e-05</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.001148074635187696</v>
+        <v>-0.004946118642333866</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.0002396740466527492</v>
+        <v>-0.0001992561105207125</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>-0.0002487562189054715</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.002451111136628872</v>
+        <v>-0.0007749866381613707</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.002752538749331931</v>
+        <v>-0.0041631347749019</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.0009329805269234575</v>
+        <v>-0.0006899715847998505</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.985122210415082e-05</v>
+        <v>-0.0001612150446197197</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.005622258434261898</v>
+        <v>-0.000563475498496957</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.0005927101558350994</v>
+        <v>-0.001756697065865467</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.001465402357042445</v>
+        <v>-4.51807228915635e-05</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0003014489519032381</v>
+        <v>-0.0001846799873372829</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.001295321304719094</v>
+        <v>-0.00173879443585781</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.00134807267552306</v>
+        <v>-0.001432006485772891</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.002207904425887075</v>
+        <v>-0.0005023355653816202</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>-3.957783641160839e-05</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.0006270160591539593</v>
+        <v>-0.001344226907265045</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.000301907986546826</v>
+        <v>0</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0002065612203509815</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.001122657448941397</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.001093743245077772</v>
+        <v>0</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.0007616247995724606</v>
+        <v>-0.001151340178856133</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.001442684734316335</v>
+        <v>0.0001344348325799965</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.00227039638895557</v>
+        <v>-0.0002710843373493477</v>
       </c>
       <c r="CA6" t="n">
-        <v>-0.0001368960297753991</v>
+        <v>0.0001004598826483433</v>
       </c>
       <c r="CB6" t="n">
-        <v>1.381978993921784e-05</v>
+        <v>-5.826287883083647e-05</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.0001195536663124275</v>
+        <v>-0.0002716783361081193</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.001321259476455214</v>
+        <v>-5.027593001613595e-05</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0005603581727885249</v>
+        <v>-0.0006999017681728586</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.001191421888495919</v>
+        <v>-1.665334536937735e-17</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.0001992561105206958</v>
+        <v>-0.0005971635772759082</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0003729468953292403</v>
+        <v>-0.000196232339089461</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.0003190440704959746</v>
+        <v>-0.0001453789833320507</v>
       </c>
       <c r="CJ6" t="n">
         <v>0</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.0003257793332603759</v>
+        <v>-3.136093295235398e-05</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.001937996749251256</v>
+        <v>0</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.0002791529709542273</v>
+        <v>-0.0001202565473008899</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.0002210216110019869</v>
+        <v>-7.72797527047897e-05</v>
       </c>
       <c r="CO6" t="n">
-        <v>-0.0002405130946018297</v>
+        <v>-0.0001545763386206711</v>
       </c>
       <c r="CP6" t="n">
-        <v>-8.017103153394324e-05</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.000814291175052323</v>
+        <v>-0.0005983914576753541</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.001234176539476703</v>
+        <v>-0.0007406592239393827</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0.001979917544780641</v>
+        <v>1.009843686520795e-05</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0.002813194923983684</v>
+        <v>-0.000313971742543151</v>
       </c>
       <c r="CU6" t="n">
-        <v>-7.367387033399564e-05</v>
+        <v>0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
@@ -3383,10 +3383,10 @@
         <v>0</v>
       </c>
       <c r="CX6" t="n">
-        <v>-7.849293563577108e-05</v>
+        <v>-0.0007112242065479862</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0.002470612474873801</v>
+        <v>-0.0001622658458526605</v>
       </c>
       <c r="CZ6" t="n">
         <v>0</v>
@@ -3395,49 +3395,49 @@
         <v>0</v>
       </c>
       <c r="DB6" t="n">
-        <v>-9.353287012293377e-05</v>
+        <v>-3.924646781787722e-05</v>
       </c>
       <c r="DC6" t="n">
-        <v>-0.000849521504939127</v>
+        <v>-0.0008834868926757833</v>
       </c>
       <c r="DD6" t="n">
-        <v>-5.265999235090635e-05</v>
+        <v>-5.296547455111156e-05</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.001356581607180665</v>
+        <v>-0.0007940101551457468</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0.0002210216110019869</v>
+        <v>-0.0008785202955537946</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0.003086584714056662</v>
+        <v>-0.001520604202143328</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.001067593275504933</v>
+        <v>-0.001317886215572545</v>
       </c>
       <c r="DJ6" t="n">
         <v>0</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0.001137388453618055</v>
+        <v>-0.0005464815705342435</v>
       </c>
       <c r="DL6" t="n">
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0.001018705392214697</v>
+        <v>-0.0003783715364638008</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0.001241290212231425</v>
+        <v>-0.0008062340221387743</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.0005187687683423425</v>
+        <v>-0.00110153907748457</v>
       </c>
       <c r="DP6" t="n">
-        <v>-0.001424802110817969</v>
+        <v>-0.0005210801742910248</v>
       </c>
       <c r="DQ6" t="n">
         <v>0</v>
@@ -3449,10 +3449,10 @@
         <v>0</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0.001156627890146353</v>
+        <v>-0.0003985122210414416</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0.0003166226912928672</v>
+        <v>-0.001188813338124794</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
@@ -3464,43 +3464,43 @@
         <v>0</v>
       </c>
       <c r="DY6" t="n">
-        <v>-0.002846973141094616</v>
+        <v>-0.001292519604638664</v>
       </c>
       <c r="DZ6" t="n">
         <v>0</v>
       </c>
       <c r="EA6" t="n">
-        <v>0</v>
+        <v>-0.0005611972207376025</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.0003693200005121161</v>
+        <v>-0.0004839057958678838</v>
       </c>
       <c r="EC6" t="n">
-        <v>-0.0005601818620268762</v>
+        <v>-3.552156175645196e-05</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0.0001026404241721679</v>
+        <v>-7.849293563578775e-05</v>
       </c>
       <c r="EE6" t="n">
         <v>0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.001466921180378023</v>
+        <v>-0.000271696643008551</v>
       </c>
       <c r="EG6" t="n">
-        <v>-4.008551576697162e-05</v>
+        <v>0</v>
       </c>
       <c r="EH6" t="n">
         <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.0002318392581143691</v>
+        <v>-3.68369351669895e-05</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.0002606321330101274</v>
+        <v>0</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.0001815438280495574</v>
+        <v>-7.849293563578775e-05</v>
       </c>
       <c r="EL6" t="n">
         <v>0</v>
@@ -3518,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0.0003141869649358253</v>
+        <v>-0.0001243781094527357</v>
       </c>
       <c r="ER6" t="n">
         <v>0</v>
@@ -3530,16 +3530,16 @@
         <v>0</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0.0004787470484843681</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-8.017103153394324e-05</v>
+        <v>-0.0002769381767249418</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0.0002805986103688013</v>
+        <v>0</v>
       </c>
       <c r="EY6" t="n">
         <v>0</v>
@@ -3552,311 +3552,311 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0002530959327196769</v>
+        <v>0.0002923876251568425</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>9.823182711197199e-05</v>
+        <v>0.0001067989948932979</v>
       </c>
       <c r="E7" t="n">
-        <v>9.881422924900019e-05</v>
+        <v>0.0002085805673706753</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4557956777993e-05</v>
+        <v>5.142723449023667e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001277618284771703</v>
+        <v>0.0002074465687442795</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0001888975456466935</v>
+        <v>0.0005293447996433387</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0002588072418575893</v>
+        <v>0.0002638522427440726</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0008273216162341723</v>
+        <v>-0.0001059054113543345</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-4.911591355598599e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0003543006844196062</v>
+        <v>0.0001905410365825699</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.00146740918850411</v>
+        <v>0.0003663003663004205</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0009499667914315447</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0002834832206993099</v>
+        <v>-7.849293563578774e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.001681997900742488</v>
+        <v>0.001071694795220424</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.00015940488841657</v>
+        <v>-2.763957987838572e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004623681686032222</v>
+        <v>0.0002561433067362007</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0002104564874891024</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-7.915567282321679e-05</v>
+        <v>2.47035573122667e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>-6.024096385543465e-05</v>
+        <v>1.665334536937735e-17</v>
       </c>
       <c r="X7" t="n">
-        <v>0.000542459057129735</v>
+        <v>0.0003579705215659256</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.656748140278387e-05</v>
+        <v>0.0002432717116008565</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0002110817941952448</v>
+        <v>0.00010319649294806</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0005439835298693074</v>
+        <v>0.000161017566513244</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.001852014350718029</v>
+        <v>-2.830559385103015e-06</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.003953674987529593</v>
+        <v>0.005740559199891565</v>
       </c>
       <c r="AF7" t="n">
-        <v>-7.849293563577664e-05</v>
+        <v>0.000247035573122556</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0001381978993919286</v>
+        <v>0.000170799283368972</v>
       </c>
       <c r="AH7" t="n">
-        <v>-7.961166623455252e-05</v>
+        <v>0.0002601977077512529</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>0.0002638522427440781</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.003116013837890313</v>
+        <v>0.003865585185153941</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.00942705331114892</v>
+        <v>0.005523218876149721</v>
       </c>
       <c r="AL7" t="n">
-        <v>-1.665334536937735e-17</v>
+        <v>2.616431187861257e-05</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0003915662650602281</v>
+        <v>0.001273598276146531</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.4557956777993e-05</v>
+        <v>-0.0001105583195135429</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.001160142955828791</v>
+        <v>0.0005351754621709336</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.763957987838572e-05</v>
+        <v>0.00013453428859031</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.006101011304493009</v>
+        <v>0.00811619088595263</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.0002258294541630568</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.000763833306890327</v>
+        <v>-0.0001549629739979907</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.0002819644123992049</v>
+        <v>-0.0001381978993919286</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.0007690945503017188</v>
+        <v>-0.0001860503815351133</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.0007058749092555717</v>
+        <v>0.0002439997142721417</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.0007938792011480289</v>
+        <v>-6.408722745516183e-05</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-7.541405030578877e-05</v>
+        <v>5.277044854881119e-05</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.001649563024410367</v>
+        <v>0.0007583378906878824</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.0008284324633626661</v>
+        <v>0.0004859013891979847</v>
       </c>
       <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>-0.0004238039025457107</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.0001204819277108693</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-0.0001431597034905752</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0.0003167939292123445</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.0004619854664236867</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.0005036884315387568</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>2.638522427441114e-05</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0.0002902374670184782</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>-2.763957987838572e-05</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>8.18466411595331e-05</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>-0.0003929273084479212</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>8.166438403117704e-05</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0.0001870657402458842</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.0002033728581873839</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>-5.551115123125783e-18</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0.0003109444727064259</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0.000107607783513991</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0.0005108878158666286</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>7.952759655222575e-05</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.0004848738537460484</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0.0001569858712716032</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>2.638522427440559e-05</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.0002699632079301185</v>
+      </c>
+      <c r="CI7" t="n">
         <v>-2.575991756826323e-05</v>
       </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>-0.0007749866381614346</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>-0.0004234179439944807</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0.0004145936981757858</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>0.0002888003090304736</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>0.001031539091690126</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.000131926121372028</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>-7.36738703340012e-05</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0.0001549480117221225</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>-0.0001068947087119354</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>-0.001010007954585762</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>0.0005919892801901694</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>0.0001264538091273859</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>2.763957987838572e-05</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>-0.0005431261047840863</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>-2.455795677799855e-05</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>0.0001204819277108304</v>
-      </c>
-      <c r="BY7" t="n">
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.0002255010965783233</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0.00015940488841657</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>7.727975270478971e-05</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>-5.151983513652647e-05</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>-0.000147347740667958</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>-0.0001658374792703143</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0.0003559398041444783</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>2.638522427440559e-05</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
         <v>-5.277044854881119e-05</v>
       </c>
-      <c r="BZ7" t="n">
-        <v>-0.0009789871550783813</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>0.0004301857562727162</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>0.000255627190903801</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>7.703218106946407e-05</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>-0.0003307590558402462</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>-1.665334536937735e-17</v>
-      </c>
-      <c r="CF7" t="n">
-        <v>-7.978097952935914e-05</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>-2.441235624374704e-05</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>-2.616431187859592e-05</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>-0.000131926121372028</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>5.402480415279132e-05</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ7" t="n">
-        <v>-0.0001227897838899927</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>-8.041002842719691e-05</v>
-      </c>
-      <c r="CS7" t="n">
-        <v>-0.0002690194587849082</v>
-      </c>
-      <c r="CT7" t="n">
-        <v>-0.0006618176924004182</v>
-      </c>
-      <c r="CU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX7" t="n">
-        <v>5.527915975677145e-05</v>
-      </c>
-      <c r="CY7" t="n">
-        <v>-0.0002487562189054715</v>
-      </c>
       <c r="CZ7" t="n">
         <v>0</v>
       </c>
@@ -3864,28 +3864,28 @@
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>-2.575991756826323e-05</v>
+        <v>5.344735435596215e-05</v>
       </c>
       <c r="DC7" t="n">
-        <v>-0.0002061017848275615</v>
+        <v>-0.0002669974872332448</v>
       </c>
       <c r="DD7" t="n">
         <v>0</v>
       </c>
       <c r="DE7" t="n">
-        <v>2.638522427440559e-05</v>
+        <v>7.915567282321679e-05</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.0006583051324852874</v>
+        <v>-5.527915975677145e-05</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.0006640886211776387</v>
+        <v>-0.0001964636542239551</v>
       </c>
       <c r="DI7" t="n">
-        <v>-7.36738703340012e-05</v>
+        <v>0.0005710328658954878</v>
       </c>
       <c r="DJ7" t="n">
         <v>0</v>
@@ -3897,16 +3897,16 @@
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.0001870657402458675</v>
+        <v>0</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0.0003796977549129055</v>
+        <v>-7.352826979971637e-05</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0002520805740089726</v>
+        <v>-0.0001381978993919286</v>
       </c>
       <c r="DP7" t="n">
-        <v>7.970244420830719e-05</v>
+        <v>0.0004625456363292812</v>
       </c>
       <c r="DQ7" t="n">
         <v>0</v>
@@ -3918,10 +3918,10 @@
         <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.0002043551263466226</v>
+        <v>0.0001352473633923768</v>
       </c>
       <c r="DU7" t="n">
-        <v>2.470355731225005e-05</v>
+        <v>-0.0004020501421359846</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
@@ -3933,19 +3933,19 @@
         <v>0</v>
       </c>
       <c r="DY7" t="n">
-        <v>-0.001826594960169814</v>
+        <v>-0.000391566265060217</v>
       </c>
       <c r="DZ7" t="n">
         <v>0</v>
       </c>
       <c r="EA7" t="n">
-        <v>2.4557956777993e-05</v>
+        <v>0</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.0002355910983512399</v>
+        <v>0.0006149727076216804</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0004552647906968576</v>
+        <v>0.0008152501161684589</v>
       </c>
       <c r="ED7" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="EF7" t="n">
-        <v>0</v>
+        <v>-6.0240963855418e-05</v>
       </c>
       <c r="EG7" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>0</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>7.367387033399564e-05</v>
       </c>
       <c r="ER7" t="n">
         <v>0</v>
@@ -3999,13 +3999,13 @@
         <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>0</v>
+        <v>7.849293563580995e-05</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0</v>
+        <v>-5.151983513652647e-05</v>
       </c>
       <c r="EX7" t="n">
         <v>0</v>
@@ -4021,298 +4021,298 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001120848768599689</v>
+        <v>0.0009010416259883303</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0006463799556805094</v>
+        <v>0.0002347261172250481</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0002763007707587084</v>
+        <v>0.001057790345664766</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0001032414045672586</v>
+        <v>0.0003670380003002877</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00282149574940703</v>
+        <v>0.002132367152312581</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003562005277044755</v>
+        <v>0.001587415791050267</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002627635942281367</v>
+        <v>0.0008830519513231105</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0004353562005276923</v>
+        <v>0.0002710843373494226</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002441910367704941</v>
+        <v>0.0001159196290571846</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002239165561942702</v>
+        <v>0.0001243781094527357</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0007611540690123569</v>
+        <v>0.001212712009014197</v>
       </c>
       <c r="N8" t="n">
-        <v>-7.530120481928359e-05</v>
+        <v>0.001066070993610113</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00118477562191891</v>
+        <v>0.0001420839409357888</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0006500540420256051</v>
+        <v>0.0001202565473008899</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0007228828955791716</v>
+        <v>0.002727015479344738</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0008634692086200157</v>
+        <v>0.0003460093900653049</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00200712901923033</v>
+        <v>0.0009748441103613753</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>5.381114847370638e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.0005494505494505724</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0008241758241758546</v>
+        <v>0.0003449740887117469</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0004258463086758119</v>
+        <v>0.0005287036168555414</v>
       </c>
       <c r="X8" t="n">
-        <v>0.00154103141160418</v>
+        <v>0.0008606670120529708</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>0.000320684126135773</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0002106399694036365</v>
+        <v>0.001383112846766163</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0006760415609030013</v>
+        <v>0.0006786630045580943</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.00120256547300904</v>
+        <v>0.0002223320158103004</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.001770324331809126</v>
+        <v>0.0008466533166404084</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.007691051846046255</v>
+        <v>0.009654437177729158</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.005817659160080715</v>
+        <v>0.01135717941101126</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.000761137340227605</v>
+        <v>0.0008592971720953885</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0006317097003281175</v>
+        <v>0.0008845232456106438</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0003957783641160839</v>
+        <v>0.0005187687683423425</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0005580771545266982</v>
+        <v>0.001563293810928518</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.00615311346683198</v>
+        <v>0.009615721841827334</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.01550390888900966</v>
+        <v>0.01322936690196366</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0008340797780512999</v>
+        <v>0.0007065738838425124</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.002602729567318693</v>
+        <v>0.004950711938663785</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0003428325416437172</v>
+        <v>0.0004006922509504823</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.002659543622604332</v>
+        <v>0.001273555804237864</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0002611071267689086</v>
+        <v>0.0001464208591795163</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0003789781279293581</v>
+        <v>0.0006949318597695459</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.009327098563934613</v>
+        <v>0.01077886299580385</v>
       </c>
       <c r="AS8" t="n">
-        <v>-1.308215593928963e-05</v>
+        <v>0.0001986385184309131</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.002570255582395792</v>
+        <v>0.0004671835809189839</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.0005841604439395742</v>
+        <v>0.000502318392581133</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.0001719056974459815</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.002531096682637296</v>
+        <v>0.0007790574409961392</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>0.0003091190108191588</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0003854861070143323</v>
+        <v>0.0006045759997047012</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.0004760942567813731</v>
+        <v>0.000301907986546826</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.001902798942806758</v>
+        <v>0.001313712075707929</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.001863090673116616</v>
+        <v>0.002272979907227199</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.900051283075636e-05</v>
+        <v>0.0002805986103688013</v>
       </c>
       <c r="BD8" t="n">
-        <v>9.0361445783127e-05</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.734621796593236e-05</v>
+        <v>0.00037313432835821</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.001175472641554332</v>
+        <v>0.001088574748130244</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.0009164166578763177</v>
+        <v>9.797339576794739e-05</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.000746676994321202</v>
+        <v>0.0003299845298818799</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.005943133229677841</v>
+        <v>0.0007398655999730136</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.003103305890938918</v>
+        <v>0.001618520408592455</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0008493222869006112</v>
+        <v>0.0009473547455909725</v>
       </c>
       <c r="BL8" t="n">
         <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.001073173290175611</v>
+        <v>0.0009072816928464206</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.00122960883385648</v>
+        <v>0.0009122272092109613</v>
       </c>
       <c r="BO8" t="n">
-        <v>-3.143022516087224e-05</v>
+        <v>0.0006279434850863686</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.001661446655131771</v>
+        <v>0.0002564733029449401</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.001291837624361333</v>
+        <v>0.0002003369208057743</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.001128206673975682</v>
+        <v>0.001042223409941173</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0004274088438185302</v>
+        <v>0.0005157646063504939</v>
       </c>
       <c r="BU8" t="n">
-        <v>7.849293563581272e-05</v>
+        <v>0.0002618640311818104</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>0.0008743078691461875</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0003959322104235607</v>
+        <v>4.145936981757859e-05</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0005741893217296983</v>
+        <v>0.0006021795429308279</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0001925781588336728</v>
+        <v>0.001487512376173522</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0007947597956532243</v>
+        <v>0.0006647635870422581</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.001253420495650692</v>
+        <v>0.0004245186014126185</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.001299332266498218</v>
+        <v>0.0008811784658848881</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.000135942365484501</v>
+        <v>0.001356444472846466</v>
       </c>
       <c r="CE8" t="n">
-        <v>3.683693516697284e-05</v>
+        <v>0.0005131495927498426</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.000213075900459947</v>
+        <v>0.0004089547112454184</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0003600378655605419</v>
+        <v>0.0001159196290571846</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0002620399596068551</v>
+        <v>0.000338029577702928</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.000147347740667958</v>
+        <v>0.0004477079791838368</v>
       </c>
       <c r="CJ8" t="n">
         <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>4.145936981757859e-05</v>
+        <v>0.001056411385182243</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0005315096731239255</v>
+        <v>0.0003823955364700649</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.000180722891566254</v>
+        <v>0.0003279118917286883</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0004307943235391993</v>
+        <v>9.628057822415326e-05</v>
       </c>
       <c r="CO8" t="n">
-        <v>3.683693516699227e-05</v>
+        <v>0</v>
       </c>
       <c r="CP8" t="n">
         <v>0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0</v>
+        <v>0.0001482213438735336</v>
       </c>
       <c r="CR8" t="n">
-        <v>-1.308215593929241e-05</v>
+        <v>0.0001037232843721425</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.957783641160839e-05</v>
+        <v>0.0007630122473653633</v>
       </c>
       <c r="CT8" t="n">
-        <v>0</v>
+        <v>0.000180944729683985</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>0.0002537968353031606</v>
       </c>
       <c r="CV8" t="n">
         <v>0</v>
@@ -4321,10 +4321,10 @@
         <v>0</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.0008189321132594075</v>
+        <v>0.0001583113456464502</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.0002105699001093531</v>
+        <v>0.0001944107275137247</v>
       </c>
       <c r="CZ8" t="n">
         <v>0</v>
@@ -4333,34 +4333,34 @@
         <v>0</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>0.0001435592089355703</v>
       </c>
       <c r="DC8" t="n">
-        <v>0</v>
+        <v>0.0002770448548812671</v>
       </c>
       <c r="DD8" t="n">
-        <v>5.336925646835522e-05</v>
+        <v>0</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0005663738174440935</v>
+        <v>0.0004361369499962603</v>
       </c>
       <c r="DF8" t="n">
-        <v>-7.547681151939267e-05</v>
+        <v>0.0002901270108205595</v>
       </c>
       <c r="DG8" t="n">
-        <v>8.017103153391825e-05</v>
+        <v>0.0003957783641161228</v>
       </c>
       <c r="DH8" t="n">
-        <v>-0.0001204819277108554</v>
+        <v>0.001053727304014149</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0004782146652497682</v>
+        <v>0.001906223045361466</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.0006143648924438333</v>
+        <v>0</v>
       </c>
       <c r="DK8" t="n">
-        <v>0</v>
+        <v>0.0002578585461689847</v>
       </c>
       <c r="DL8" t="n">
         <v>0</v>
@@ -4369,28 +4369,28 @@
         <v>0</v>
       </c>
       <c r="DN8" t="n">
-        <v>-2.672367717798663e-05</v>
+        <v>0.0005490392529030303</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.001076355289694278</v>
+        <v>0.0004776678938646417</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.0004811116791973186</v>
+        <v>0.001436893165914099</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0</v>
+        <v>5.29654745510949e-05</v>
       </c>
       <c r="DR8" t="n">
         <v>0</v>
       </c>
       <c r="DS8" t="n">
-        <v>3.957783641160839e-05</v>
+        <v>7.970244420828497e-05</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.0003735847952784338</v>
+        <v>0.0009833431008462678</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.000472186091375465</v>
+        <v>0.0001720512979802469</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
@@ -4399,44 +4399,44 @@
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.0001852766798418753</v>
+        <v>0.0001594048884165699</v>
       </c>
       <c r="DY8" t="n">
-        <v>-2.759206586583628e-05</v>
+        <v>0.0004731705158144695</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0</v>
+        <v>0.0001202565473009148</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.0003817906802981552</v>
+        <v>0.000185276679841917</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0002223320158102476</v>
+        <v>0.000888112686457987</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0007981926761959857</v>
+        <v>0.001181354214418939</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0001300911821098316</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
         <v>0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0</v>
+        <v>7.915567282321679e-05</v>
       </c>
       <c r="EG8" t="n">
         <v>0</v>
       </c>
       <c r="EH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0.0002789585547289975</v>
+      </c>
+      <c r="EJ8" t="n">
         <v>3.92464678179022e-05</v>
       </c>
-      <c r="EI8" t="n">
-        <v>0.0001701784834088199</v>
-      </c>
-      <c r="EJ8" t="n">
-        <v>0</v>
-      </c>
       <c r="EK8" t="n">
         <v>0</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>3.92464678179022e-05</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
         <v>0</v>
@@ -4453,10 +4453,10 @@
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>3.924646781791052e-05</v>
+        <v>0</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0002527034648766996</v>
+        <v>0.0002117335121737729</v>
       </c>
       <c r="ER8" t="n">
         <v>0</v>
@@ -4465,10 +4465,10 @@
         <v>0</v>
       </c>
       <c r="ET8" t="n">
-        <v>4.51807228915635e-05</v>
+        <v>0</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>0.0008871841535717877</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
@@ -4477,10 +4477,10 @@
         <v>0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0002747252747253154</v>
+        <v>0.000239107332624855</v>
       </c>
       <c r="EY8" t="n">
-        <v>0</v>
+        <v>0.0002789585547289975</v>
       </c>
     </row>
     <row r="9">
@@ -4490,466 +4490,466 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01112828438948993</v>
+        <v>0.013086038124678</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000180722891566254</v>
+        <v>0.000497512437810943</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003819989534275303</v>
+        <v>0.0006413682522715458</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004604918890633236</v>
+        <v>0.007322287546766393</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0005232862375720293</v>
+        <v>0.002266872746007176</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004115446285408863</v>
+        <v>0.004018547140649154</v>
       </c>
       <c r="H9" t="n">
-        <v>0.004133961276818476</v>
+        <v>0.004430705821741376</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009943328181349787</v>
+        <v>0.004197662061636564</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001647183846971334</v>
+        <v>0.005151983513652758</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002084446819882368</v>
+        <v>0.0003438113948919685</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0006024096385541799</v>
+        <v>0.0002575991756826324</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00244420828905425</v>
+        <v>0.002763018065887335</v>
       </c>
       <c r="N9" t="n">
-        <v>0.004636785162287438</v>
+        <v>0.0108191653786708</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00577231427044359</v>
+        <v>0.002005277044854936</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002163833075734112</v>
+        <v>0.001688654353562058</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.004552590266876022</v>
+        <v>0.007418856259659967</v>
       </c>
       <c r="R9" t="n">
-        <v>0.005599162742019925</v>
+        <v>0.0005421686746988619</v>
       </c>
       <c r="S9" t="n">
-        <v>0.005860805860805884</v>
+        <v>0.006594538897475521</v>
       </c>
       <c r="T9" t="n">
+        <v>0.003741314804917106</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.002512025654730043</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.002679031427099421</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.001603420630678831</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.01123132405976301</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.001443078567610856</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.005685441020191295</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.004675876726886274</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.000978876867594003</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.002163833075734134</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.01512560128273648</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.01561051004636785</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.00223166843783208</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.002405130946018119</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.001883830455259072</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.003580972741849231</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.01213163064833012</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.02782071097372488</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.003142709943328193</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.04662545079855746</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.004430705821741388</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.00694815606627468</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.0002638522427440559</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.004729011689691809</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.02081401339515714</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.001098901098901117</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.001603095632946372</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.001213720316622757</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.0007212776919113706</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.001184956208140109</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.0009620523784072299</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.00468830499742402</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.002163833075734134</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.006233900051519814</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.01318907779495105</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.0004709576138148264</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.0004810261892036594</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.00087583719732095</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.006070120355834685</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.00206079340546107</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0.001854714064914953</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.01901081916537865</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.002627511591962906</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.006734366648850831</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.0007326007326007745</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.002357563850687683</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0.005203503348789285</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.001086956521739213</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.0008840864440078589</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.001424802110818002</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0.003192534381139522</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0.003099946552645594</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.0007727975270478971</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.001854714064914964</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0.0004709576138148264</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0.0007438894792773487</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0.004552590266876044</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.003580972741849242</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0.00160342063067882</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0.002458578300374081</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.001442555383822741</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.002616431187859813</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.001647183846971301</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.0008840864440078922</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.001178781925343819</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.002266872746007187</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.002975557917109439</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0.002191341528594393</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0.004489577765900555</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0.0006876227897839038</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0.0007482629609833924</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.0008017103153394433</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.0008551576696953167</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.0003929273084479767</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0.003099946552645616</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0.001229289150187018</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0.001924104756814582</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0.0001068947087119021</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0.001229289150187041</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.002244788882950244</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>5.151983513652647e-05</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.0003206841261357729</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0.0003929273084479435</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0.0007367387033399119</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0.0004911591355599376</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0.0004940711462451119</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0.001175841795831045</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0.001443078567610867</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.004222340994120766</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.002832709780865805</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0.0008970976253298458</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0.001333992094861725</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0.0005344735435596215</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0.0007915567282322123</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>0.001988487702773467</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0.002093144950287851</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.0001603420630678864</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>5.151983513652647e-05</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.0003693931398416894</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0.006520577231427005</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0.005505077498663779</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.0003139717425431954</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>0.001055408970976301</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.0002638522427440671</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.001647183846971278</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0.006467129877071043</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>0.004430705821741376</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0.0006860158311345899</v>
+      </c>
+      <c r="EE9" t="n">
         <v>0.0003606388459556853</v>
       </c>
-      <c r="U9" t="n">
-        <v>0.001328374070138194</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.003241232731137134</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.001806588735387937</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.006520577231427039</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.000374131480491724</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.003760947964966455</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.005398182789951888</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0.003297269448737716</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.002298236237306228</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.01251931993817614</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.01482213438735178</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.00321899736147756</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.002618920363441956</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.001603420630678742</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0.002354788069073843</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.0099705304518664</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0.0367336424523441</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0.003503348789283833</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.04667697063369395</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0.004276146316331752</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0.004329235702832701</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0.001569858712715921</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0.003046499198289665</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0.01767130345182891</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0.0003206841261357174</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0.006852138073158131</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0.001222104144527148</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.0007849293563579884</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.005128205128205154</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0.0003091190108191588</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0.002215352910870638</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.001988487702773467</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0.006388459556929382</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0.02081401339515709</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0.0002672367717797664</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0.001443078567610867</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0.0012650602409638</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0.00716902145473578</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>0.006027820710973697</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>0.001389631213254949</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>0.01622874806800616</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.005255023183925789</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0.008912931478619223</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0.002885110767645483</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0.004447933019361638</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>0.004430705821741321</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>0.001465201465201504</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>0.006697578567748552</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>0.003313253012048168</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>0.00510046367851621</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>0.001175841795831056</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>0.003313253012048145</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>0.0001569858712716199</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>0.001084337349397524</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>0.0009564293304995197</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>0.005808477237048704</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>0.002878074306645773</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0.002730551262235903</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>0.002030999465526417</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>0.001977552111170455</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>0.008925708177445212</v>
-      </c>
-      <c r="CE9" t="n">
-        <v>0.001336183858898965</v>
-      </c>
-      <c r="CF9" t="n">
-        <v>0.0006876227897838593</v>
-      </c>
-      <c r="CG9" t="n">
-        <v>0.002228915662650566</v>
-      </c>
-      <c r="CH9" t="n">
-        <v>0.003313735970069465</v>
-      </c>
-      <c r="CI9" t="n">
-        <v>0.002228915662650566</v>
-      </c>
-      <c r="CJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>0.0005151983513652536</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>0.001906233900051479</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>0.00324437467294616</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>0.001912858660998951</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>0.001098901098901139</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ9" t="n">
-        <v>0.001870657402458553</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>0.009353287012292877</v>
-      </c>
-      <c r="CS9" t="n">
-        <v>0.005615662029881496</v>
-      </c>
-      <c r="CT9" t="n">
-        <v>0.0006633499170812573</v>
-      </c>
-      <c r="CU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX9" t="n">
-        <v>0.004436130411544603</v>
-      </c>
-      <c r="CY9" t="n">
-        <v>0.0005421686746987619</v>
-      </c>
-      <c r="CZ9" t="n">
-        <v>0.002112313240597585</v>
-      </c>
-      <c r="DA9" t="n">
-        <v>0.0006279434850863907</v>
-      </c>
-      <c r="DB9" t="n">
-        <v>0.0006802721088435826</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>0.0008433734939758853</v>
-      </c>
-      <c r="DD9" t="n">
-        <v>0.0001482213438735114</v>
-      </c>
-      <c r="DE9" t="n">
-        <v>0.001831501831501892</v>
-      </c>
-      <c r="DF9" t="n">
-        <v>0.0003458498023715117</v>
-      </c>
-      <c r="DG9" t="n">
-        <v>0.001569858712715899</v>
-      </c>
-      <c r="DH9" t="n">
-        <v>0.0006279434850863907</v>
-      </c>
-      <c r="DI9" t="n">
-        <v>0.00423861852433286</v>
-      </c>
-      <c r="DJ9" t="n">
-        <v>0.001336183858898932</v>
-      </c>
-      <c r="DK9" t="n">
-        <v>0.001854714064914953</v>
-      </c>
-      <c r="DL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM9" t="n">
-        <v>0.003297269448737705</v>
-      </c>
-      <c r="DN9" t="n">
-        <v>0.0003458498023715006</v>
-      </c>
-      <c r="DO9" t="n">
-        <v>0.004290947148090052</v>
-      </c>
-      <c r="DP9" t="n">
-        <v>0.002407116692831035</v>
-      </c>
-      <c r="DQ9" t="n">
+      <c r="EF9" t="n">
+        <v>0.0003719447396386633</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>0.0002638522427440559</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.0007482629609834701</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>0.0007970244420828831</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0.0003206841261357729</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0.0003206841261357729</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>9.823182711199419e-05</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>5.313496280552332e-05</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>0.0009273570324574764</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>0.0004810261892035927</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0.0008243173621844235</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0.001870657402458609</v>
+      </c>
+      <c r="EV9" t="n">
         <v>0.0002672367717797552</v>
       </c>
-      <c r="DR9" t="n">
-        <v>0.000963855421686688</v>
-      </c>
-      <c r="DS9" t="n">
-        <v>0.0005421686746987619</v>
-      </c>
-      <c r="DT9" t="n">
-        <v>0.001936159079016286</v>
-      </c>
-      <c r="DU9" t="n">
-        <v>0.002930402930402987</v>
-      </c>
-      <c r="DV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW9" t="n">
-        <v>0.0001105583195135429</v>
-      </c>
-      <c r="DX9" t="n">
-        <v>0.003741314804917151</v>
-      </c>
-      <c r="DY9" t="n">
-        <v>0.003976975405546879</v>
-      </c>
-      <c r="DZ9" t="n">
-        <v>0.000361445783132508</v>
-      </c>
-      <c r="EA9" t="n">
-        <v>0.001496525921966829</v>
-      </c>
-      <c r="EB9" t="n">
-        <v>0.004395604395604424</v>
-      </c>
-      <c r="EC9" t="n">
-        <v>0.003349031920460543</v>
-      </c>
-      <c r="ED9" t="n">
-        <v>0.0007438894792774042</v>
-      </c>
-      <c r="EE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF9" t="n">
-        <v>0.0008243173621844235</v>
-      </c>
-      <c r="EG9" t="n">
-        <v>3.330669073875469e-17</v>
-      </c>
-      <c r="EH9" t="n">
-        <v>0.0003091190108191588</v>
-      </c>
-      <c r="EI9" t="n">
-        <v>0.002072263549415554</v>
-      </c>
-      <c r="EJ9" t="n">
-        <v>0.0007438894792774154</v>
-      </c>
-      <c r="EK9" t="n">
-        <v>0.001445783132530087</v>
-      </c>
-      <c r="EL9" t="n">
-        <v>5.232862375720293e-05</v>
-      </c>
-      <c r="EM9" t="n">
-        <v>0.0002137894174238486</v>
-      </c>
-      <c r="EN9" t="n">
-        <v>0.0001658374792703143</v>
-      </c>
-      <c r="EO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="EP9" t="n">
-        <v>0.0005313496280552998</v>
-      </c>
-      <c r="EQ9" t="n">
-        <v>0.001626506024096353</v>
-      </c>
-      <c r="ER9" t="n">
-        <v>0</v>
-      </c>
-      <c r="ES9" t="n">
-        <v>0.0003139717425432176</v>
-      </c>
-      <c r="ET9" t="n">
-        <v>0.0004422332780541716</v>
-      </c>
-      <c r="EU9" t="n">
-        <v>0.002710843373493932</v>
-      </c>
-      <c r="EV9" t="n">
-        <v>0</v>
-      </c>
       <c r="EW9" t="n">
-        <v>0.0003206841261357285</v>
+        <v>0.0001583113456464558</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.000963855421686699</v>
+        <v>0.0003606388459556853</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0003166226912928672</v>
+        <v>0.0009881422924902239</v>
       </c>
     </row>
   </sheetData>
